--- a/artfynd/S 2895-2022 artfynd.xlsx
+++ b/artfynd/S 2895-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY255"/>
+  <dimension ref="A1:AZ255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17278188</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17278512</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -994,6 +1009,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466008</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466009</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1198,6 +1223,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466010</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1300,6 +1330,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466011</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1402,6 +1437,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466012</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1504,6 +1544,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466013</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1601,6 +1646,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466014</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1698,6 +1748,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466015</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1795,6 +1850,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466016</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1892,6 +1952,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466017</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1989,6 +2054,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466018</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2086,6 +2156,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466019</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2183,6 +2258,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466020</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2280,6 +2360,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466021</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2381,6 +2466,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114358654</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2482,6 +2572,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114358661</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2583,6 +2678,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114358663</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2680,6 +2780,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114358666</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2777,6 +2882,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114358668</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2874,6 +2984,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114358670</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2971,6 +3086,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114358671</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3068,6 +3188,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114358672</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3165,6 +3290,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114358676</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3262,6 +3392,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114358677</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3359,6 +3494,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114358678</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3456,6 +3596,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114358679</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3553,6 +3698,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114358681</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3650,6 +3800,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114358682</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3747,6 +3902,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114358683</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3844,6 +4004,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114358684</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3941,6 +4106,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114358653</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4038,6 +4208,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114358675</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4135,6 +4310,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114358658</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4232,6 +4412,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114358656</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4351,6 +4536,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128037826</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4461,6 +4651,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17278514</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4562,6 +4757,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114358659</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4659,6 +4859,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114358662</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4760,6 +4965,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114358669</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4857,6 +5067,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114358652</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4954,6 +5169,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114358667</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5051,6 +5271,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114358673</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5148,6 +5373,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114358674</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5258,6 +5488,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17278520</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5355,6 +5590,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114358655</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5452,6 +5692,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114358680</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5568,6 +5813,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92779962</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5684,6 +5934,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92779990</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5797,6 +6052,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92732356</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5918,6 +6178,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92733356</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6044,6 +6309,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92779934</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6142,6 +6412,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92822580</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6240,6 +6515,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92822757</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6360,6 +6640,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92780001</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6458,6 +6743,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93097284</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6556,6 +6846,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92822352</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6672,6 +6967,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112434492</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6792,6 +7092,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115554563</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6912,6 +7217,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115554472</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7032,6 +7342,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115554488</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7138,6 +7453,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92645724</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7244,6 +7564,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92645830</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7350,6 +7675,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92645861</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7466,6 +7796,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99768591</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7572,6 +7907,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107581309</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7678,6 +8018,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107581470</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7784,6 +8129,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107581631</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7890,6 +8240,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107581718</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7996,6 +8351,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107581763</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8102,6 +8462,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107581879</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8208,6 +8573,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107581962</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8314,6 +8684,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107582017</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8429,6 +8804,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/140654</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8544,6 +8924,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/140655</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8651,6 +9036,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/141081</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8748,6 +9138,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/141082</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8859,6 +9254,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/142149</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8969,6 +9369,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16217313</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9079,6 +9484,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16217317</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9189,6 +9599,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16217321</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9299,6 +9714,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16217326</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9409,6 +9829,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16217347</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9519,6 +9944,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16217353</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9629,6 +10059,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16217367</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9733,6 +10168,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56518683</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9837,6 +10277,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56518684</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9941,6 +10386,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56518685</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10045,6 +10495,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56518686</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10149,6 +10604,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56518687</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10246,6 +10706,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466037</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10343,6 +10808,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466038</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10440,6 +10910,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466039</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10537,6 +11012,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466040</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10639,6 +11119,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466041</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10736,6 +11221,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466042</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10838,6 +11328,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466043</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10940,6 +11435,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466044</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11037,6 +11537,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466045</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11134,6 +11639,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466046</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11236,6 +11746,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466047</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11333,6 +11848,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466048</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11430,6 +11950,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466049</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11527,6 +12052,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466050</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11624,6 +12154,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466051</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11721,6 +12256,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466052</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11818,6 +12358,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466053</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11915,6 +12460,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466054</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12012,6 +12562,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466055</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12109,6 +12664,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466056</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12211,6 +12771,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466057</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12308,6 +12873,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466058</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12410,6 +12980,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466059</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12512,6 +13087,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466060</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12609,6 +13189,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466061</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12711,6 +13296,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466062</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12808,6 +13398,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466063</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12905,6 +13500,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466064</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13002,6 +13602,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466065</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13099,6 +13704,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466066</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13196,6 +13806,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466067</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13293,6 +13908,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466068</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13390,6 +14010,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466069</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13487,6 +14112,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466070</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13584,6 +14214,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466071</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13681,6 +14316,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466072</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13778,6 +14418,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466073</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13875,6 +14520,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466074</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13972,6 +14622,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466075</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14069,6 +14724,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466093</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14166,6 +14826,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466094</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14268,6 +14933,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111090994</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14375,6 +15045,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118584961</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14477,6 +15152,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118646739</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14579,6 +15259,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129520025</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14681,6 +15366,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129520027</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14783,6 +15473,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129520028</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14894,6 +15589,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131009084</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15002,6 +15702,11 @@
       <c r="AY141" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17278210</t>
         </is>
       </c>
     </row>
@@ -15105,6 +15810,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129520024</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15205,6 +15915,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60254361</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15303,6 +16018,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92695938</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15428,6 +16148,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91948876</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15554,6 +16279,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109006212</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15652,6 +16382,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92637235</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15783,6 +16518,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115864627</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -15885,6 +16625,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109899975</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -15992,6 +16737,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110523108</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -16094,6 +16844,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129520026</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -16196,6 +16951,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129520022</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -16296,6 +17056,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65369160</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -16417,6 +17182,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92645929</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -16539,6 +17309,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88109092</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -16648,6 +17423,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91990241</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -16771,6 +17551,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99768486</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -16894,6 +17679,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107832755</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -17013,6 +17803,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115869248</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -17136,6 +17931,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123373601</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -17259,6 +18059,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123373670</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -17382,6 +18187,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123540947</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -17491,6 +18301,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131066572</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -17591,6 +18406,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60254357</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -17700,6 +18520,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91990249</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -17809,6 +18634,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107581781</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -17932,6 +18762,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107832773</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -18045,6 +18880,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114510832</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -18154,6 +18994,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115353754</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -18269,6 +19114,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99768776</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -18382,6 +19232,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96038666</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -18495,6 +19350,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131066560</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -18606,6 +19466,11 @@
           <t>Fiskinventering med eDNA</t>
         </is>
       </c>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130942687</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -18717,6 +19582,11 @@
           <t>Fiskinventering med eDNA</t>
         </is>
       </c>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130942670</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -18834,6 +19704,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91948912</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -18946,6 +19821,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91948946</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -19058,6 +19938,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107305029</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -19155,6 +20040,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117184512</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -19274,6 +20164,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121514291</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -19391,6 +20286,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109295664</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -19515,6 +20415,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121514275</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -19632,6 +20537,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109295442</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -19751,6 +20661,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99768731</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -19868,6 +20783,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109295674</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -19985,6 +20905,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109295805</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -20107,6 +21032,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109296434</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -20224,6 +21154,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109297062</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -20333,6 +21268,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107582341</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -20452,6 +21392,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107832796</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -20571,6 +21516,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115332308</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -20682,6 +21632,11 @@
           <t>Fiskinventering med eDNA</t>
         </is>
       </c>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130942589</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -20779,6 +21734,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466032</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -20876,6 +21836,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466033</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -20973,6 +21938,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466034</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -21075,6 +22045,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4818445</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -21177,6 +22152,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129520029</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -21279,6 +22259,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129520032</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -21381,6 +22366,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5285414</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -21491,6 +22481,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17278411</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -21617,6 +22612,11 @@
           <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61697916</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -21714,6 +22714,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466025</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -21811,6 +22816,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466026</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -21908,6 +22918,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466027</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -22005,6 +23020,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466028</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -22102,6 +23122,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466029</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -22199,6 +23224,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466030</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -22325,6 +23355,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92938689</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -22443,6 +23478,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16217310</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -22547,6 +23587,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56518688</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -22644,6 +23689,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466035</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -22741,6 +23791,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466036</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -22838,6 +23893,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466076</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -22935,6 +23995,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466077</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -23032,6 +24097,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466078</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -23129,6 +24199,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466079</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -23226,6 +24301,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466080</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -23323,6 +24403,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466081</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -23420,6 +24505,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466082</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -23517,6 +24607,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466086</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -23614,6 +24709,11 @@
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466087</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -23711,6 +24811,11 @@
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466088</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -23808,6 +24913,11 @@
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466091</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -23905,6 +25015,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466092</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -24003,6 +25118,11 @@
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92696679</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -24128,6 +25248,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96036913</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -24249,6 +25374,11 @@
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96036985</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -24356,6 +25486,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125493256</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -24477,6 +25612,11 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96030011</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -24591,6 +25731,11 @@
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134435847</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -24707,6 +25852,11 @@
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109675405</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -24806,6 +25956,11 @@
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54011404</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -24922,6 +26077,11 @@
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109659687</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -25032,6 +26192,11 @@
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134435817</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -25156,6 +26321,11 @@
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124297994</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -25271,6 +26441,11 @@
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124023496</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -25381,6 +26556,11 @@
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94601327</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -25488,6 +26668,11 @@
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125493287</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -25593,6 +26778,11 @@
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16821791</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -25715,6 +26905,11 @@
           <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16980420</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -25825,6 +27020,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83642230</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -25938,6 +27138,11 @@
       <c r="AY241" t="inlineStr">
         <is>
           <t>Trädportalen</t>
+        </is>
+      </c>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83642233</t>
         </is>
       </c>
     </row>
@@ -26042,6 +27247,11 @@
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93121549</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -26139,6 +27349,11 @@
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466031</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -26241,6 +27456,11 @@
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118646771</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -26343,6 +27563,11 @@
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71985294</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -26445,6 +27670,11 @@
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118646761</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -26550,6 +27780,11 @@
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16821802</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -26672,6 +27907,11 @@
           <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16980421</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -26787,6 +28027,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83642232</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -26895,6 +28140,11 @@
       <c r="AY250" t="inlineStr">
         <is>
           <t>Trädportalen</t>
+        </is>
+      </c>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83642235</t>
         </is>
       </c>
     </row>
@@ -26999,6 +28249,11 @@
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93121551</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -27108,6 +28363,11 @@
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94603048</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -27205,6 +28465,11 @@
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466023</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -27302,6 +28567,11 @@
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104466024</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -27404,8 +28674,269 @@
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118646745</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>